--- a/output/focus_stocks.xlsx
+++ b/output/focus_stocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
   <si>
     <t>Stock_Name</t>
   </si>
@@ -40,12 +40,12 @@
     <t>Score</t>
   </si>
   <si>
+    <t>华电辽能</t>
+  </si>
+  <si>
     <t>中南文化</t>
   </si>
   <si>
-    <t>华电辽能</t>
-  </si>
-  <si>
     <t>深华发Ａ</t>
   </si>
   <si>
@@ -58,10 +58,19 @@
     <t>韶能股份</t>
   </si>
   <si>
+    <t>汉缆股份</t>
+  </si>
+  <si>
     <t>卓郎智能</t>
   </si>
   <si>
-    <t>汉缆股份</t>
+    <t>东方新能</t>
+  </si>
+  <si>
+    <t>金开新能</t>
+  </si>
+  <si>
+    <t>正泰电源</t>
   </si>
   <si>
     <t>山东墨龙</t>
@@ -73,22 +82,25 @@
     <t>绿发电力</t>
   </si>
   <si>
-    <t>金开新能</t>
-  </si>
-  <si>
     <t>新锦动力</t>
   </si>
   <si>
+    <t>节能风电</t>
+  </si>
+  <si>
     <t>通光线缆</t>
   </si>
   <si>
-    <t>正泰电源</t>
-  </si>
-  <si>
     <t>德石股份</t>
   </si>
   <si>
-    <t>东方新能</t>
+    <t>华塑控股</t>
+  </si>
+  <si>
+    <t>奥瑞德</t>
+  </si>
+  <si>
+    <t>粤电力Ａ</t>
   </si>
   <si>
     <t>泰嘉股份</t>
@@ -103,48 +115,42 @@
     <t>协鑫能科</t>
   </si>
   <si>
-    <t>节能风电</t>
-  </si>
-  <si>
-    <t>华塑控股</t>
-  </si>
-  <si>
-    <t>奥瑞德</t>
-  </si>
-  <si>
     <t>黄河旋风</t>
   </si>
   <si>
+    <t>浙江新能</t>
+  </si>
+  <si>
+    <t>拓日新能</t>
+  </si>
+  <si>
     <t>智能自控</t>
   </si>
   <si>
-    <t>粤电力Ａ</t>
-  </si>
-  <si>
     <t>三星医疗</t>
   </si>
   <si>
     <t>长城科技</t>
   </si>
   <si>
+    <t>公用事业</t>
+  </si>
+  <si>
     <t>机械设备</t>
   </si>
   <si>
-    <t>公用事业</t>
-  </si>
-  <si>
     <t>电子</t>
   </si>
   <si>
     <t>电力设备</t>
   </si>
   <si>
+    <t>电力</t>
+  </si>
+  <si>
     <t>通用设备</t>
   </si>
   <si>
-    <t>电力</t>
-  </si>
-  <si>
     <t>光学光电子</t>
   </si>
   <si>
@@ -154,10 +160,10 @@
     <t>专用设备</t>
   </si>
   <si>
+    <t>火力发电</t>
+  </si>
+  <si>
     <t>机床工具</t>
-  </si>
-  <si>
-    <t>火力发电</t>
   </si>
   <si>
     <t>面板</t>
@@ -173,16 +179,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -198,7 +196,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -206,30 +204,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,32 +504,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -558,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="H2">
-        <v>30.15687417984008</v>
+        <v>56.13000831604005</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -584,25 +564,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>10.02</v>
+        <v>10.04</v>
       </c>
       <c r="H3">
-        <v>30.05365705490112</v>
+        <v>35.14339733123779</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -610,13 +590,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -636,13 +616,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5">
         <v>6</v>
@@ -662,13 +642,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -688,16 +668,16 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -706,7 +686,7 @@
         <v>9.98</v>
       </c>
       <c r="H7">
-        <v>14.96803207397461</v>
+        <v>17.95575399398804</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -714,13 +694,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -729,10 +709,10 @@
         <v>3</v>
       </c>
       <c r="G8">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="H8">
-        <v>14.9477783203125</v>
+        <v>14.96685476303101</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -743,13 +723,13 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -758,7 +738,7 @@
         <v>9.970000000000001</v>
       </c>
       <c r="H9">
-        <v>11.96685476303101</v>
+        <v>14.9477783203125</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -766,25 +746,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="H10">
-        <v>9.020282936096191</v>
+        <v>12.06451606750488</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -792,25 +772,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="H11">
-        <v>9.002515697479248</v>
+        <v>10.02087173461914</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -818,25 +798,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12">
         <v>10</v>
       </c>
       <c r="H12">
-        <v>8.996310138702393</v>
+        <v>10.00334644317627</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -844,25 +824,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13">
         <v>10.02</v>
       </c>
       <c r="H13">
-        <v>8.012919425964355</v>
+        <v>9.020282936096191</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -870,25 +850,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14">
-        <v>20.03</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>8.010490036010742</v>
+        <v>9.002515697479248</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -896,25 +876,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>20.01</v>
+        <v>10</v>
       </c>
       <c r="H15">
-        <v>8.004474258422851</v>
+        <v>8.996310138702393</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -922,25 +902,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>2</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>20.03</v>
       </c>
       <c r="H16">
-        <v>8.00219955444336</v>
+        <v>8.010490036010742</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -948,25 +928,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17">
-        <v>20</v>
+        <v>10.01</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>8.005583000183105</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -974,25 +954,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>2</v>
       </c>
       <c r="G18">
-        <v>10.05</v>
+        <v>20.01</v>
       </c>
       <c r="H18">
-        <v>6.031516456604003</v>
+        <v>8.004474258422851</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1000,25 +980,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>2</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19">
-        <v>10.01</v>
+        <v>20</v>
       </c>
       <c r="H19">
-        <v>6.004743289947509</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1026,25 +1006,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H20">
-        <v>6.000251197814941</v>
+        <v>7.973833274841309</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1052,25 +1032,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H21">
-        <v>5.998566627502441</v>
+        <v>7.969478797912598</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1078,13 +1058,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E22">
         <v>3</v>
@@ -1093,10 +1073,10 @@
         <v>2</v>
       </c>
       <c r="G22">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="H22">
-        <v>5.995379447937012</v>
+        <v>6.009421920776368</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1104,25 +1084,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G23">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="H23">
-        <v>5.987645912170409</v>
+        <v>6.004743289947509</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1130,13 +1110,13 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E24">
         <v>3</v>
@@ -1145,10 +1125,10 @@
         <v>2</v>
       </c>
       <c r="G24">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>5.968943214416504</v>
+        <v>6.000251197814941</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1156,13 +1136,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1171,10 +1151,10 @@
         <v>2</v>
       </c>
       <c r="G25">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>5.951130294799805</v>
+        <v>5.998566627502441</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1182,25 +1162,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26">
         <v>2</v>
       </c>
       <c r="G26">
-        <v>10.03</v>
+        <v>9.99</v>
       </c>
       <c r="H26">
-        <v>4.012701797485351</v>
+        <v>5.995379447937012</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1208,13 +1188,13 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -1223,10 +1203,10 @@
         <v>2</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="H27">
-        <v>4</v>
+        <v>4.012701797485351</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1234,13 +1214,13 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -1249,10 +1229,10 @@
         <v>2</v>
       </c>
       <c r="G28">
-        <v>9.99</v>
+        <v>10.03</v>
       </c>
       <c r="H28">
-        <v>3.99643497467041</v>
+        <v>4.011524963378906</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1260,13 +1240,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -1275,10 +1255,10 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="H29">
-        <v>3.996328163146972</v>
+        <v>4.006373977661132</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1301,9 +1281,61 @@
         <v>2</v>
       </c>
       <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31">
+        <v>2</v>
+      </c>
+      <c r="F31">
+        <v>2</v>
+      </c>
+      <c r="G31">
         <v>9.99</v>
       </c>
-      <c r="H30">
+      <c r="H31">
+        <v>3.996328163146972</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>9.99</v>
+      </c>
+      <c r="H32">
         <v>3.995397758483887</v>
       </c>
     </row>

--- a/output/focus_stocks.xlsx
+++ b/output/focus_stocks.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="56">
   <si>
     <t>Stock_Name</t>
   </si>
@@ -46,15 +46,15 @@
     <t>中南文化</t>
   </si>
   <si>
+    <t>华电能源</t>
+  </si>
+  <si>
     <t>深华发Ａ</t>
   </si>
   <si>
     <t>顺钠股份</t>
   </si>
   <si>
-    <t>华电能源</t>
-  </si>
-  <si>
     <t>韶能股份</t>
   </si>
   <si>
@@ -73,21 +73,30 @@
     <t>正泰电源</t>
   </si>
   <si>
+    <t>节能风电</t>
+  </si>
+  <si>
+    <t>奥瑞德</t>
+  </si>
+  <si>
     <t>山东墨龙</t>
   </si>
   <si>
+    <t>浙江新能</t>
+  </si>
+  <si>
     <t>华盛昌</t>
   </si>
   <si>
     <t>绿发电力</t>
   </si>
   <si>
+    <t>粤电力Ａ</t>
+  </si>
+  <si>
     <t>新锦动力</t>
   </si>
   <si>
-    <t>节能风电</t>
-  </si>
-  <si>
     <t>通光线缆</t>
   </si>
   <si>
@@ -97,15 +106,12 @@
     <t>华塑控股</t>
   </si>
   <si>
-    <t>奥瑞德</t>
-  </si>
-  <si>
-    <t>粤电力Ａ</t>
-  </si>
-  <si>
     <t>泰嘉股份</t>
   </si>
   <si>
+    <t>新能泰山</t>
+  </si>
+  <si>
     <t>积成电子</t>
   </si>
   <si>
@@ -118,7 +124,7 @@
     <t>黄河旋风</t>
   </si>
   <si>
-    <t>浙江新能</t>
+    <t>宁波能源</t>
   </si>
   <si>
     <t>拓日新能</t>
@@ -131,6 +137,9 @@
   </si>
   <si>
     <t>长城科技</t>
+  </si>
+  <si>
+    <t>湖南发展</t>
   </si>
   <si>
     <t>公用事业</t>
@@ -504,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -538,25 +547,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
         <v>8</v>
-      </c>
-      <c r="F2">
-        <v>7</v>
       </c>
       <c r="G2">
         <v>10.02</v>
       </c>
       <c r="H2">
-        <v>56.13000831604005</v>
+        <v>72.1696891784668</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -564,13 +573,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -590,25 +599,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4">
         <v>9.99</v>
       </c>
       <c r="H4">
-        <v>24.98517656326294</v>
+        <v>27.97307319641114</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -616,25 +625,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5">
-        <v>10.01</v>
+        <v>9.99</v>
       </c>
       <c r="H5">
-        <v>24.02167167663574</v>
+        <v>24.98517656326294</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -642,13 +651,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E6">
         <v>6</v>
@@ -657,10 +666,10 @@
         <v>4</v>
       </c>
       <c r="G6">
-        <v>9.99</v>
+        <v>10.01</v>
       </c>
       <c r="H6">
-        <v>23.96591758728027</v>
+        <v>24.02167167663574</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -668,25 +677,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <v>9.98</v>
+        <v>9.99</v>
       </c>
       <c r="H7">
-        <v>17.95575399398804</v>
+        <v>20.97064218521118</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -694,13 +703,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -720,13 +729,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E9">
         <v>5</v>
@@ -746,13 +755,13 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>4</v>
@@ -772,13 +781,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -798,13 +807,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>5</v>
@@ -824,25 +833,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="H13">
-        <v>9.020282936096191</v>
+        <v>10.00150966644287</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -850,25 +859,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H14">
-        <v>9.002515697479248</v>
+        <v>9.969478797912597</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -876,13 +885,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -891,10 +900,10 @@
         <v>3</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="H15">
-        <v>8.996310138702393</v>
+        <v>9.020282936096191</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -902,25 +911,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>20.03</v>
+        <v>10.01</v>
       </c>
       <c r="H16">
-        <v>8.010490036010742</v>
+        <v>9.007152271270753</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -928,25 +937,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17">
-        <v>10.01</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>8.005583000183105</v>
+        <v>9.002515697479248</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -963,16 +972,16 @@
         <v>51</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18">
-        <v>20.01</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>8.004474258422851</v>
+        <v>8.996310138702393</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -980,25 +989,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19">
         <v>2</v>
       </c>
       <c r="G19">
-        <v>20</v>
+        <v>10.02</v>
       </c>
       <c r="H19">
-        <v>8</v>
+        <v>8.01532154083252</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1006,25 +1015,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>2</v>
       </c>
       <c r="G20">
-        <v>9.970000000000001</v>
+        <v>20.03</v>
       </c>
       <c r="H20">
-        <v>7.973833274841309</v>
+        <v>8.010490036010742</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1032,25 +1041,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <v>2</v>
       </c>
       <c r="G21">
-        <v>9.960000000000001</v>
+        <v>20.01</v>
       </c>
       <c r="H21">
-        <v>7.969478797912598</v>
+        <v>8.004474258422851</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1058,25 +1067,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>2</v>
       </c>
       <c r="G22">
-        <v>10.02</v>
+        <v>20</v>
       </c>
       <c r="H22">
-        <v>6.009421920776368</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1084,25 +1093,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G23">
-        <v>10.01</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="H23">
-        <v>6.004743289947509</v>
+        <v>7.973833274841309</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1110,25 +1119,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>10.01</v>
       </c>
       <c r="H24">
-        <v>6.000251197814941</v>
+        <v>6.004743289947509</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1136,13 +1145,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E25">
         <v>3</v>
@@ -1154,7 +1163,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>5.998566627502441</v>
+        <v>6.001952934265137</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1162,13 +1171,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D26" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E26">
         <v>3</v>
@@ -1177,10 +1186,10 @@
         <v>2</v>
       </c>
       <c r="G26">
-        <v>9.99</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>5.995379447937012</v>
+        <v>6.000251197814941</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1188,25 +1197,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="H27">
-        <v>4.012701797485351</v>
+        <v>5.998566627502441</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1214,25 +1223,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>2</v>
       </c>
       <c r="G28">
-        <v>10.03</v>
+        <v>9.99</v>
       </c>
       <c r="H28">
-        <v>4.011524963378906</v>
+        <v>5.995379447937012</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1240,13 +1249,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -1255,10 +1264,10 @@
         <v>2</v>
       </c>
       <c r="G29">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="H29">
-        <v>4.006373977661132</v>
+        <v>4.012701797485351</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1266,13 +1275,13 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -1281,10 +1290,10 @@
         <v>2</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="H30">
-        <v>4</v>
+        <v>4.009569358825684</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1307,10 +1316,10 @@
         <v>2</v>
       </c>
       <c r="G31">
-        <v>9.99</v>
+        <v>10.02</v>
       </c>
       <c r="H31">
-        <v>3.996328163146972</v>
+        <v>4.006373977661132</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1318,25 +1327,103 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32">
+        <v>2</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32">
+        <v>10</v>
+      </c>
+      <c r="H32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33">
+        <v>9.99</v>
+      </c>
+      <c r="H33">
+        <v>3.996328163146972</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="F34">
+        <v>2</v>
+      </c>
+      <c r="G34">
+        <v>9.99</v>
+      </c>
+      <c r="H34">
+        <v>3.995397758483887</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
         <v>42</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C35" t="s">
         <v>46</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D35" t="s">
         <v>51</v>
       </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="F32">
-        <v>2</v>
-      </c>
-      <c r="G32">
-        <v>9.99</v>
-      </c>
-      <c r="H32">
-        <v>3.995397758483887</v>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35">
+        <v>9.98</v>
+      </c>
+      <c r="H35">
+        <v>3.992853927612305</v>
       </c>
     </row>
   </sheetData>
